--- a/public/data/NuclearMedicineDemoDatabase.xlsx
+++ b/public/data/NuclearMedicineDemoDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\nuclear-medicine-guide\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82838138-128E-4D18-8021-A1CB8FF89F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57393FB8-1FFD-4F4C-BC2B-708DA66103DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="1" r:id="rId1"/>
@@ -1722,7 +1722,9 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12">
+        <v>6</v>
+      </c>
       <c r="B16" s="11" t="s">
         <v>18</v>
       </c>
@@ -2689,7 +2691,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>117</v>
@@ -2727,7 +2729,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>173</v>
@@ -2777,7 +2779,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>169</v>
@@ -2815,7 +2817,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>136</v>
@@ -3005,7 +3007,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>117</v>
@@ -3055,7 +3057,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>190</v>
@@ -3105,7 +3107,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>197</v>
@@ -3143,7 +3145,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>155</v>
@@ -3181,7 +3183,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>211</v>
@@ -3219,7 +3221,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>199</v>
@@ -3257,7 +3259,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>155</v>
@@ -3295,7 +3297,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>117</v>
@@ -3333,7 +3335,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>236</v>
@@ -3383,7 +3385,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>214</v>
@@ -3433,7 +3435,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>136</v>
@@ -3623,7 +3625,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>117</v>
@@ -3661,7 +3663,7 @@
         <v>30</v>
       </c>
       <c r="B41" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>230</v>
@@ -3711,7 +3713,7 @@
         <v>30</v>
       </c>
       <c r="B42" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>169</v>
@@ -3749,7 +3751,7 @@
         <v>30</v>
       </c>
       <c r="B43" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>136</v>
@@ -3977,7 +3979,7 @@
         <v>26</v>
       </c>
       <c r="B50" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>241</v>
@@ -4015,7 +4017,7 @@
         <v>26</v>
       </c>
       <c r="B51" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>128</v>
@@ -4053,7 +4055,7 @@
         <v>26</v>
       </c>
       <c r="B52" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>136</v>
